--- a/technician_forms/015_installation_check_form--technician_forms.xlsx
+++ b/technician_forms/015_installation_check_form--technician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -988,8 +988,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'system1'}</t>
+          <t>system1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'system1'}</t>
+          <t>system1</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'system2'}</t>
+          <t>system2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'system2'}</t>
+          <t>system2</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'system3'}</t>
+          <t>system3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'system3'}</t>
+          <t>system3</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'service1'}</t>
+          <t>service1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'service1'}</t>
+          <t>service1</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'service2'}</t>
+          <t>service2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'service2'}</t>
+          <t>service2</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'service3'}</t>
+          <t>service3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'service3'}</t>
+          <t>service3</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'system1'}</t>
+          <t>system1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'system1'}</t>
+          <t>system1</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'system2'}</t>
+          <t>system2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'system2'}</t>
+          <t>system2</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'system3'}</t>
+          <t>system3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'system3'}</t>
+          <t>system3</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'service1'}</t>
+          <t>service1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'service1'}</t>
+          <t>service1</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'service2'}</t>
+          <t>service2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'service2'}</t>
+          <t>service2</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'service3'}</t>
+          <t>service3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'service3'}</t>
+          <t>service3</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'active'}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'active'}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'active'}</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
